--- a/2026 Conference Ranks.xlsx
+++ b/2026 Conference Ranks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigoc\Documents\AU\Machine Learning\analytics_challenge\analytics_challenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358297A0-1567-4D6E-B9C7-83722821F2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB0ECD2-0B27-4FF3-A3F0-D55C042DE0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10290" yWindow="0" windowWidth="10524" windowHeight="12318" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -471,90 +471,90 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
         <v>5</v>
-      </c>
-      <c r="B6">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7">
         <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
         <v>7</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9">
         <v>8</v>
-      </c>
-      <c r="B9">
-        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
         <v>9</v>
-      </c>
-      <c r="B10">
-        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11">
         <v>10</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12">
         <v>11</v>
-      </c>
-      <c r="B12">
-        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
         <v>12</v>
-      </c>
-      <c r="B13">
-        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -567,149 +567,152 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B16">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17">
         <v>16</v>
-      </c>
-      <c r="B17">
-        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
         <v>17</v>
-      </c>
-      <c r="B18">
-        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19">
         <v>18</v>
-      </c>
-      <c r="B19">
-        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20">
         <v>19</v>
-      </c>
-      <c r="B20">
-        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21">
         <v>20</v>
-      </c>
-      <c r="B21">
-        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22">
         <v>21</v>
-      </c>
-      <c r="B22">
-        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23">
         <v>22</v>
-      </c>
-      <c r="B23">
-        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24">
         <v>23</v>
-      </c>
-      <c r="B24">
-        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25">
         <v>24</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26">
         <v>25</v>
-      </c>
-      <c r="B26">
-        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27">
         <v>26</v>
-      </c>
-      <c r="B27">
-        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28">
         <v>27</v>
-      </c>
-      <c r="B28">
-        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29">
         <v>28</v>
-      </c>
-      <c r="B29">
-        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30">
         <v>29</v>
-      </c>
-      <c r="B30">
-        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31">
         <v>30</v>
-      </c>
-      <c r="B31">
-        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32">
         <v>31</v>
       </c>
-      <c r="B32">
-        <v>11</v>
-      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B32">
+    <sortCondition ref="B2:B32"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>